--- a/光伏配储项目/电价数据/2026/梅县站.xlsx
+++ b/光伏配储项目/电价数据/2026/梅县站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.43505</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7841</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50368</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24136</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.14118</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.07193000000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51174</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14301</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.35632</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6667000000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8888200000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21419</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.3462</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17901</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.02888</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30791</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.40885</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70475</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.75619</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.1185</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9501900000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.90884</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80655</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7686799999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51863</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48939</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46938</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43082</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73029</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90622</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9693200000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51195</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53949</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51916</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5193099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50069</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.49911</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.53081</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.42448</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.41489</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.54061</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5547799999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49661</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.03123</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.03799</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18554</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.02964</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.59035</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60188</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7661</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18643</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.38784</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13977</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.85956</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22691</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12417</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.08722</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.8438600000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.10842</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66759</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00175</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9267300000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.97846</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81226</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45424</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3354</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52113</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49912</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45464</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44749</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22229</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.03594</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79671</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44391</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32086</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62826</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66601</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50722</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50449</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62858</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34294</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5230199999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.0361</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.04241</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18515</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6413</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47438</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52181</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50464</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33056</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.07628</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03722</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.06259000000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.06428</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.07615999999999999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.11621</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.08807999999999999</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.08853</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.14545</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.26068</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.21968</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.16983</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.06206</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.15191</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.19033</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.18062</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.14105</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.17044</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.17602</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.15826</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.13195</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.17526</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.02759</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10149</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00594</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19843</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04539</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14076</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01033</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05258</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.23199</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.21949</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.16395</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33533</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.14792</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46066</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7857499999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86974</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61426</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55641</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.21175</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.22447</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.22553</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.21006</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.15693</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.18516</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>-0.01641</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89164</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47667</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.75154</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24412</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.09736</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.25283</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.10947</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.13831</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.25109</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.02853</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.00212</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.05393999999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.06737</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.17757</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.05274</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.15369</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.08017000000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.08583</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.17672</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.73852</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.04918</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-0.03749</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-0.02562</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.09923</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.12752</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.03373</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.15548</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.08343</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.16531</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.07077</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.03646</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.12774</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.18528</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.11602</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.14541</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09637000000000001</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25222</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26016</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20418</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.15029</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.18546</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.23848</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.17068</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.10624</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.07514</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.12289</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.15088</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.16195</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.09246</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.14241</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.07531</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.01196</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.14455</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.19224</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.20358</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.09268000000000001</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.18781</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.64561</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32972</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.04965</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.5559700000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.6498400000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="R126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.24698</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.21603</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.22939</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.24683</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.23656</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.18633</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.13096</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.12043</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.23008</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.16939</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.19831</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.09806000000000001</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.18662</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.23165</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.23954</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.19396</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.15463</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.19537</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.09526999999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.10001</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.009630000000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.01811</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.20582</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.19115</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.18514</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.02789</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.17804</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.10857</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.19369</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.01378</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>-0.01657</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.09376999999999999</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.10027</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.15802</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.14852</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.14451</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.14412</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.13988</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.16776</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.10866</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02368</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.00455</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.02046</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04567</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04731</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.11316</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>-0.04809</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.08267000000000001</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>-0.04082</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.21785</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>-0.04873</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.21152</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.20244</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.19306</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.03468</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>-0.02099</v>
+      </c>
+      <c r="R128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.04228</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.02616</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.05256</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.05619</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.10934</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.04828</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.10953</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.10441</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.10678</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.18026</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.20588</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.16439</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.23001</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23532</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18275</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14281</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.14652</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17863</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21687</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.08771</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.25276</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.12454</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.02855</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.06258</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.01982</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.13859</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.16516</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.19188</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.18497</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.12061</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.08045000000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.13145</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.14063</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.14119</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.06335</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.06265999999999999</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.18635</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.10223</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>-0.04025</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.08202</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.03436</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.21874</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.02305</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.19363</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-0.02831</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.06464</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-0.0372</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.02792</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.05271</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.16988</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.06134000000000001</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.16611</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.16157</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.07282999999999999</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.16287</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.15821</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.06587999999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.02922</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>-0.03999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.16326</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.07396999999999999</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9638600000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.50948</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.20532</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.19794</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.18838</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.19332</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.09595999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.19387</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.20718</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.17096</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.22094</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.14157</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.08025</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.20884</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.14544</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.16569</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.20278</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.43623</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.21687</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.5415599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.21042</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.19473</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.07498</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.09206</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.13129</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>-0.03756</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-0.02009</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-0.00062</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-0.00421</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="R130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.14314</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.14632</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.03595</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.17899</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.20468</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.20709</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.17093</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.17141</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.08578</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.02314</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.04688000000000001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.13894</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.07246</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.10545</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.07514</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.16931</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.10167</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.15574</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.05727</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.06559000000000001</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.06764000000000001</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.09253</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.17222</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.14882</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>-0.02063</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.06808</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.08906</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.17865</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.07601999999999999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.16865</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.18208</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.18326</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.19411</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.17807</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.19095</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.17138</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.05908</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.17205</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.17209</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.17302</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.1679</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.16869</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-0.00647</v>
+      </c>
+      <c r="O131" t="n">
+        <v>-0.03167</v>
+      </c>
+      <c r="P131" t="n">
+        <v>-0.04043</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.16124</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.16171</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.14604</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="X131" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.03074</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.16671</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.02778</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>-0.00635</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.15798</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>-0.01567</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>-0.03576</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>-0.01227</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.02707</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.11744</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.15639</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.19389</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.21481</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.23387</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.24681</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.19376</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.20159</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.09259999999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.22375</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.27411</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.24935</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.21263</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.19049</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.11919</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.23322</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.19879</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.13259</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.15263</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.14319</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.19171</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.17162</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.10104</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.17412</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.10008</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.18044</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.18571</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.17038</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.05666</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.02709</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.19746</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.47663</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.17787</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.18079</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.16122</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.19809</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.18385</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.18066</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.18383</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.17991</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.18078</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.17464</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.18179</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.07436</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.17793</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.17388</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.07352</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.18161</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.16935</v>
+      </c>
+      <c r="V132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.18188</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.18188</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>-0.03953</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.18769</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.20169</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.17837</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.17828</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.17299</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.17368</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.17972</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.20689</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.14426</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>-0.02271</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.03807</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20415</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.04864</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15162</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2137</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.23442</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.18503</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.1375</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.13274</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.18059</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.24853</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.22091</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.19436</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.49651</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6602</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.19825</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.06763</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.08841</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.21794</v>
+      </c>
+      <c r="O133" t="n">
+        <v>-0.04417</v>
+      </c>
+      <c r="P133" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>-0.00108</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.21131</v>
+      </c>
+      <c r="S133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.24154</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.00633</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.17349</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.19681</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.19373</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6580499999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7219800000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16119</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.19735</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.11344</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.17178</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.17019</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.07316</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.18402</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.5912000000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>-0.00209</v>
+      </c>
+      <c r="R134" t="n">
+        <v>-0.03191</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.18341</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.18021</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.18919</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.18919</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.20274</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.18461</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.17838</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.20273</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.19661</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.22882</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.22277</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>-0.0363</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.20995</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.10364</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.19734</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.01879</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02611</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.03273</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.13593</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2176</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.01159</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.03637</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.21519</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.24071</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.23127</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.04118</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.20164</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.18351</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.18497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.16228</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.17469</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.13586</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.17442</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.08864</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25497</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.22562</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16182</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.05725</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.06977999999999999</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>-0.04693</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.13847</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-0.01999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-0.03157</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-0.02095</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.15934</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.09905</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15609</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02271</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01429</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03832</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01151</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20795</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.12801</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.17807</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.14631</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.08378000000000001</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.17822</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.17084</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.09146</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.09334999999999999</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.16943</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.03954999999999999</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>-0.01811</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.17426</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.01447</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.11273</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>-0.01975</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.09576999999999999</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.07239</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.01417</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.15973</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.17904</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.71497</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87153</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03929999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16746</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00227</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.20313</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>-0.02425</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.13165</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.07884000000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>-0.02248</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.8030900000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.66543</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6636799999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.6677999999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.7642100000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.13269</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.09584999999999999</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.20179</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>-0.03526</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>-0.03542</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.21066</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.15095</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.06294</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.09633</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.07590000000000001</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12352</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04821</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10901</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.19319</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.22344</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.20817</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.22482</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.20994</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.17029</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.20292</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.15545</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.18564</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.12823</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.08743000000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.11881</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.25369</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>-0.03149</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-0.03912</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-0.01644</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.01874</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.17894</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.05907</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.07787999999999999</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.17449</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.04840999999999999</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.02898</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.04507</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.05284000000000001</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.05291</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.01701</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.02888</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.06973</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.05074</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>-0.01672</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.21387</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.18744</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.14166</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.18501</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.19746</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.17351</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.23726</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.20901</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.24508</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.64718</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83065</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>-0.03276</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.20165</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.18541</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.10369</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>-0.02913</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.05823</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.03544</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.04835</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.008019999999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-0.04125</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-0.00683</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.08545999999999999</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.19839</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.09262000000000001</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.08367000000000001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.0852</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.03915999999999999</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>-0.03658</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.18957</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.06073</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.16116</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.05727</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.19051</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.17089</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43417</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.17229</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20138</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.16515</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23917</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.11762</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.11806</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.14266</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.08039</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.15262</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.18797</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.15288</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.19379</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.22764</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.12162</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45404</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6005900000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.06085</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8152200000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7174299999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>-0.03481</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>-0.03036</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.04925</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.05786</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.03372</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.01185</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.14096</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.09286</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.17073</v>
+      </c>
+      <c r="E141" t="n">
+        <v>-0.02704</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.16081</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.15398</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.15394</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.14293</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>-0.04005</v>
+      </c>
+      <c r="R141" t="n">
+        <v>-0.009010000000000001</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-0.04174</v>
+      </c>
+      <c r="U141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.14977</v>
+      </c>
+      <c r="W141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.15839</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.18633</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.18774</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.16552</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>-0.01479</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>-0.009640000000000001</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03207</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17491</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01894</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17881</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19553</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03573</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05775</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23571</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3052</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26789</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.15495</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23846</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11789</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.28078</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42722</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32571</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17677</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.0497</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17759</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15793</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24181</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22089</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20209</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15156</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41102</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.44928</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>1.40148</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>1.37076</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>1.37514</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>1.35377</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3598</v>
       </c>
     </row>
   </sheetData>
